--- a/Templates/Submersible Pump Installation.xlsx
+++ b/Templates/Submersible Pump Installation.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20325"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{59713A24-B158-4774-B5EF-7C3AF5382FBA}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -53,12 +47,15 @@
   </si>
   <si>
     <t>S &amp; F Motor starters of the following ratings Submersible pump controllers with ammeter,DPMCB for single phase 2 HP submersible motor pumps (DOL) (90.14.28.13) (Code: GWDDR134)</t>
+  </si>
+  <si>
+    <t>Installation of Single Phase Panel board where new electricity connection is required (Excluding Motor Starter) (Code: GWDDR363)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -180,7 +177,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -232,7 +229,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -426,21 +423,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F0271-4C5F-4C75-A901-BEBAC191B9A5}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="50.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -448,7 +445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -456,7 +453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -464,7 +461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -472,7 +469,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -480,7 +477,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -488,7 +485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -496,7 +493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -504,7 +501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -512,7 +509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -520,11 +517,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Templates/Submersible Pump Installation.xlsx
+++ b/Templates/Submersible Pump Installation.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20325"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{4E05254A-2DB8-49EB-AD5B-269CCC157D07}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -50,18 +56,31 @@
   </si>
   <si>
     <t>Installation of Single Phase Panel board where new electricity connection is required (Excluding Motor Starter) (Code: GWDDR363)</t>
+  </si>
+  <si>
+    <t>GI Bend 40 mm (Code: GWDMR053)</t>
+  </si>
+  <si>
+    <t>GI Socket 40 mm (Code: GWDMR057)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -106,16 +125,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,21 +448,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="50.7265625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -445,7 +470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -453,7 +478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -461,7 +486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -469,7 +494,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -477,7 +502,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -485,7 +510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -493,43 +518,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
     </row>
